--- a/Outputs_primates/AllGenes_Potential_CPDs.xlsx
+++ b/Outputs_primates/AllGenes_Potential_CPDs.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adesinamary/Documents/GitHub/kondrashov/Outputs_primates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{36ACFA73-DF46-0340-8D71-8B3B4681ADB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1074AAF9-0BC4-B749-96F9-6249F1D83E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="740" yWindow="5820" windowWidth="28040" windowHeight="17440" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
+    <workbookView xWindow="940" yWindow="12560" windowWidth="21480" windowHeight="13260" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="261">
   <si>
     <t>gene</t>
   </si>
@@ -816,18 +816,31 @@
   </si>
   <si>
     <t>NP_055610.1</t>
+  </si>
+  <si>
+    <t>orthologs</t>
+  </si>
+  <si>
+    <t>Aln</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -851,8 +864,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1187,37 +1201,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81CD1290-D98E-6145-998E-728A92BEC841}">
-  <dimension ref="A1:G129"/>
+  <dimension ref="A1:I129"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I1" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1230,17 +1250,23 @@
       <c r="D2">
         <v>29</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2">
+        <v>117</v>
+      </c>
+      <c r="F2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>9</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1253,17 +1279,20 @@
       <c r="D3">
         <v>31</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3">
+        <v>1119</v>
+      </c>
+      <c r="F3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1276,17 +1305,20 @@
       <c r="D4">
         <v>103</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4">
+        <v>191</v>
+      </c>
+      <c r="F4" t="s">
         <v>13</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>9</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1299,17 +1331,20 @@
       <c r="D5">
         <v>29</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5">
+        <v>117</v>
+      </c>
+      <c r="F5" t="s">
         <v>8</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>15</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1322,17 +1357,20 @@
       <c r="D6">
         <v>174</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6">
+        <v>221</v>
+      </c>
+      <c r="F6" t="s">
         <v>18</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>19</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1345,17 +1383,20 @@
       <c r="D7">
         <v>219</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7">
+        <v>266</v>
+      </c>
+      <c r="F7" t="s">
         <v>21</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>22</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1368,17 +1409,20 @@
       <c r="D8">
         <v>286</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8">
+        <v>333</v>
+      </c>
+      <c r="F8" t="s">
         <v>8</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>24</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1391,17 +1435,20 @@
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9">
+        <v>115</v>
+      </c>
+      <c r="F9" t="s">
         <v>19</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1414,17 +1461,20 @@
       <c r="D10">
         <v>1</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10">
+        <v>115</v>
+      </c>
+      <c r="F10" t="s">
         <v>19</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>9</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1437,17 +1487,20 @@
       <c r="D11">
         <v>15</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11">
+        <v>54</v>
+      </c>
+      <c r="F11" t="s">
         <v>11</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>21</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -1460,17 +1513,20 @@
       <c r="D12">
         <v>17</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12">
+        <v>56</v>
+      </c>
+      <c r="F12" t="s">
         <v>11</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>21</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -1483,17 +1539,20 @@
       <c r="D13">
         <v>156</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13">
+        <v>260</v>
+      </c>
+      <c r="F13" t="s">
         <v>34</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>35</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1506,17 +1565,20 @@
       <c r="D14">
         <v>260</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14">
+        <v>364</v>
+      </c>
+      <c r="F14" t="s">
         <v>37</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>38</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -1529,17 +1591,20 @@
       <c r="D15">
         <v>82</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15">
+        <v>105</v>
+      </c>
+      <c r="F15" t="s">
         <v>34</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>35</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1552,17 +1617,20 @@
       <c r="D16">
         <v>383</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16">
+        <v>397</v>
+      </c>
+      <c r="F16" t="s">
         <v>42</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>34</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1575,17 +1643,20 @@
       <c r="D17">
         <v>21</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17">
+        <v>184</v>
+      </c>
+      <c r="F17" t="s">
         <v>35</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>18</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -1598,17 +1669,20 @@
       <c r="D18">
         <v>1</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18">
+        <v>164</v>
+      </c>
+      <c r="F18" t="s">
         <v>19</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>47</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1621,17 +1695,20 @@
       <c r="D19">
         <v>2378</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19">
+        <v>3867</v>
+      </c>
+      <c r="F19" t="s">
         <v>9</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>13</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1644,17 +1721,20 @@
       <c r="D20">
         <v>1155</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20">
+        <v>2307</v>
+      </c>
+      <c r="F20" t="s">
         <v>11</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>37</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1667,17 +1747,20 @@
       <c r="D21">
         <v>1459</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21">
+        <v>2851</v>
+      </c>
+      <c r="F21" t="s">
         <v>21</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>22</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -1690,17 +1773,20 @@
       <c r="D22">
         <v>2465</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22">
+        <v>3954</v>
+      </c>
+      <c r="F22" t="s">
         <v>18</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>9</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -1713,17 +1799,20 @@
       <c r="D23">
         <v>51</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23">
+        <v>94</v>
+      </c>
+      <c r="F23" t="s">
         <v>35</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>18</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -1736,17 +1825,20 @@
       <c r="D24">
         <v>82</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24">
+        <v>128</v>
+      </c>
+      <c r="F24" t="s">
         <v>34</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>8</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>54</v>
       </c>
@@ -1759,17 +1851,20 @@
       <c r="D25">
         <v>82</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25">
+        <v>128</v>
+      </c>
+      <c r="F25" t="s">
         <v>34</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>8</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1782,17 +1877,20 @@
       <c r="D26">
         <v>85</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26">
+        <v>138</v>
+      </c>
+      <c r="F26" t="s">
         <v>47</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>21</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>54</v>
       </c>
@@ -1805,17 +1903,20 @@
       <c r="D27">
         <v>93</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27">
+        <v>155</v>
+      </c>
+      <c r="F27" t="s">
         <v>21</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>22</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>54</v>
       </c>
@@ -1828,17 +1929,20 @@
       <c r="D28">
         <v>295</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28">
+        <v>372</v>
+      </c>
+      <c r="F28" t="s">
         <v>19</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>9</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>59</v>
       </c>
@@ -1851,17 +1955,20 @@
       <c r="D29">
         <v>97</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29">
+        <v>150</v>
+      </c>
+      <c r="F29" t="s">
         <v>15</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>8</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>59</v>
       </c>
@@ -1874,17 +1981,20 @@
       <c r="D30">
         <v>85</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30">
+        <v>138</v>
+      </c>
+      <c r="F30" t="s">
         <v>37</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>11</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -1897,17 +2007,20 @@
       <c r="D31">
         <v>152</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31">
+        <v>205</v>
+      </c>
+      <c r="F31" t="s">
         <v>8</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>15</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>59</v>
       </c>
@@ -1920,17 +2033,20 @@
       <c r="D32">
         <v>95</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32">
+        <v>148</v>
+      </c>
+      <c r="F32" t="s">
         <v>8</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>63</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>65</v>
       </c>
@@ -1943,17 +2059,20 @@
       <c r="D33">
         <v>113</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33">
+        <v>158</v>
+      </c>
+      <c r="F33" t="s">
         <v>8</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>63</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>65</v>
       </c>
@@ -1966,17 +2085,20 @@
       <c r="D34">
         <v>146</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34">
+        <v>191</v>
+      </c>
+      <c r="F34" t="s">
         <v>8</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>21</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>65</v>
       </c>
@@ -1989,17 +2111,20 @@
       <c r="D35">
         <v>241</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35">
+        <v>286</v>
+      </c>
+      <c r="F35" t="s">
         <v>67</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>24</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>68</v>
       </c>
@@ -2012,17 +2137,20 @@
       <c r="D36">
         <v>969</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36">
+        <v>1102</v>
+      </c>
+      <c r="F36" t="s">
         <v>8</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>15</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>68</v>
       </c>
@@ -2035,17 +2163,20 @@
       <c r="D37">
         <v>335</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37">
+        <v>467</v>
+      </c>
+      <c r="F37" t="s">
         <v>34</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>67</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>71</v>
       </c>
@@ -2058,17 +2189,20 @@
       <c r="D38">
         <v>438</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38">
+        <v>475</v>
+      </c>
+      <c r="F38" t="s">
         <v>37</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>11</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -2081,17 +2215,20 @@
       <c r="D39">
         <v>15</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39">
+        <v>72</v>
+      </c>
+      <c r="F39" t="s">
         <v>34</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>42</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -2104,17 +2241,20 @@
       <c r="D40">
         <v>17</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40">
+        <v>74</v>
+      </c>
+      <c r="F40" t="s">
         <v>13</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>37</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>77</v>
       </c>
@@ -2127,17 +2267,20 @@
       <c r="D41">
         <v>489</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41">
+        <v>612</v>
+      </c>
+      <c r="F41" t="s">
         <v>21</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>22</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>77</v>
       </c>
@@ -2150,17 +2293,20 @@
       <c r="D42">
         <v>282</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42">
+        <v>405</v>
+      </c>
+      <c r="F42" t="s">
         <v>11</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>8</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>80</v>
       </c>
@@ -2173,17 +2319,20 @@
       <c r="D43">
         <v>65</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43">
+        <v>85</v>
+      </c>
+      <c r="F43" t="s">
         <v>11</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>9</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -2196,17 +2345,20 @@
       <c r="D44">
         <v>13</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44">
+        <v>128</v>
+      </c>
+      <c r="F44" t="s">
         <v>22</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>13</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>82</v>
       </c>
@@ -2219,17 +2371,20 @@
       <c r="D45">
         <v>1</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45">
+        <v>86</v>
+      </c>
+      <c r="F45" t="s">
         <v>19</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>8</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>86</v>
       </c>
@@ -2242,17 +2397,20 @@
       <c r="D46">
         <v>295</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E46">
+        <v>301</v>
+      </c>
+      <c r="F46" t="s">
         <v>67</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>24</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>88</v>
       </c>
@@ -2265,17 +2423,20 @@
       <c r="D47">
         <v>309</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47">
+        <v>312</v>
+      </c>
+      <c r="F47" t="s">
         <v>21</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>9</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>88</v>
       </c>
@@ -2288,17 +2449,20 @@
       <c r="D48">
         <v>296</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48">
+        <v>298</v>
+      </c>
+      <c r="F48" t="s">
         <v>47</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>22</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>91</v>
       </c>
@@ -2311,17 +2475,20 @@
       <c r="D49">
         <v>1173</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E49">
+        <v>1184</v>
+      </c>
+      <c r="F49" t="s">
         <v>35</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>21</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>93</v>
       </c>
@@ -2334,17 +2501,20 @@
       <c r="D50">
         <v>564</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50">
+        <v>594</v>
+      </c>
+      <c r="F50" t="s">
         <v>42</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>95</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>93</v>
       </c>
@@ -2357,17 +2527,20 @@
       <c r="D51">
         <v>611</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E51">
+        <v>641</v>
+      </c>
+      <c r="F51" t="s">
         <v>22</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>21</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>93</v>
       </c>
@@ -2380,17 +2553,20 @@
       <c r="D52">
         <v>539</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E52">
+        <v>569</v>
+      </c>
+      <c r="F52" t="s">
         <v>22</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>8</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>99</v>
       </c>
@@ -2403,17 +2579,17 @@
       <c r="D53">
         <v>88</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>19</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>101</v>
       </c>
-      <c r="G53" t="s">
+      <c r="H53" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>103</v>
       </c>
@@ -2426,17 +2602,20 @@
       <c r="D54">
         <v>82</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E54">
+        <v>82</v>
+      </c>
+      <c r="F54" t="s">
         <v>35</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>42</v>
       </c>
-      <c r="G54" t="s">
+      <c r="H54" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>105</v>
       </c>
@@ -2449,17 +2628,20 @@
       <c r="D55">
         <v>1042</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E55">
+        <v>1056</v>
+      </c>
+      <c r="F55" t="s">
         <v>21</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>9</v>
       </c>
-      <c r="G55" t="s">
+      <c r="H55" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -2472,17 +2654,20 @@
       <c r="D56">
         <v>2502</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E56">
+        <v>2608</v>
+      </c>
+      <c r="F56" t="s">
         <v>22</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>8</v>
       </c>
-      <c r="G56" t="s">
+      <c r="H56" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>110</v>
       </c>
@@ -2495,17 +2680,20 @@
       <c r="D57">
         <v>2038</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E57">
+        <v>2055</v>
+      </c>
+      <c r="F57" t="s">
         <v>95</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>22</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>110</v>
       </c>
@@ -2518,17 +2706,20 @@
       <c r="D58">
         <v>2157</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E58">
+        <v>2174</v>
+      </c>
+      <c r="F58" t="s">
         <v>95</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>22</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>113</v>
       </c>
@@ -2541,17 +2732,20 @@
       <c r="D59">
         <v>75</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E59">
+        <v>75</v>
+      </c>
+      <c r="F59" t="s">
         <v>8</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>15</v>
       </c>
-      <c r="G59" t="s">
+      <c r="H59" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>115</v>
       </c>
@@ -2564,17 +2758,20 @@
       <c r="D60">
         <v>936</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60">
+        <v>1122</v>
+      </c>
+      <c r="F60" t="s">
         <v>67</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
         <v>24</v>
       </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>115</v>
       </c>
@@ -2587,17 +2784,20 @@
       <c r="D61">
         <v>358</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E61">
+        <v>526</v>
+      </c>
+      <c r="F61" t="s">
         <v>9</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>8</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>117</v>
       </c>
@@ -2610,17 +2810,20 @@
       <c r="D62">
         <v>3</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E62">
+        <v>19</v>
+      </c>
+      <c r="F62" t="s">
         <v>8</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>63</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>120</v>
       </c>
@@ -2633,17 +2836,20 @@
       <c r="D63">
         <v>1</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E63">
+        <v>71</v>
+      </c>
+      <c r="F63" t="s">
         <v>19</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>18</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>122</v>
       </c>
@@ -2656,17 +2862,17 @@
       <c r="D64">
         <v>318</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>19</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
         <v>18</v>
       </c>
-      <c r="G64" t="s">
+      <c r="H64" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>122</v>
       </c>
@@ -2679,17 +2885,20 @@
       <c r="D65">
         <v>388</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E65">
+        <v>540</v>
+      </c>
+      <c r="F65" t="s">
         <v>42</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>95</v>
       </c>
-      <c r="G65" t="s">
+      <c r="H65" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>122</v>
       </c>
@@ -2702,17 +2911,20 @@
       <c r="D66">
         <v>94</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E66">
+        <v>211</v>
+      </c>
+      <c r="F66" t="s">
         <v>8</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>9</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>122</v>
       </c>
@@ -2725,17 +2937,20 @@
       <c r="D67">
         <v>496</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E67">
+        <v>648</v>
+      </c>
+      <c r="F67" t="s">
         <v>63</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>22</v>
       </c>
-      <c r="G67" t="s">
+      <c r="H67" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>122</v>
       </c>
@@ -2748,17 +2963,20 @@
       <c r="D68">
         <v>113</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E68">
+        <v>230</v>
+      </c>
+      <c r="F68" t="s">
         <v>101</v>
       </c>
-      <c r="F68" t="s">
+      <c r="G68" t="s">
         <v>18</v>
       </c>
-      <c r="G68" t="s">
+      <c r="H68" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>126</v>
       </c>
@@ -2771,17 +2989,20 @@
       <c r="D69">
         <v>223</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E69">
+        <v>249</v>
+      </c>
+      <c r="F69" t="s">
         <v>8</v>
       </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>11</v>
       </c>
-      <c r="G69" t="s">
+      <c r="H69" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>129</v>
       </c>
@@ -2794,17 +3015,20 @@
       <c r="D70">
         <v>502</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E70">
+        <v>506</v>
+      </c>
+      <c r="F70" t="s">
         <v>8</v>
       </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
         <v>38</v>
       </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>129</v>
       </c>
@@ -2817,17 +3041,20 @@
       <c r="D71">
         <v>535</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E71">
+        <v>539</v>
+      </c>
+      <c r="F71" t="s">
         <v>8</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>11</v>
       </c>
-      <c r="G71" t="s">
+      <c r="H71" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>129</v>
       </c>
@@ -2840,17 +3067,20 @@
       <c r="D72">
         <v>227</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E72">
+        <v>229</v>
+      </c>
+      <c r="F72" t="s">
         <v>95</v>
       </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
         <v>22</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>129</v>
       </c>
@@ -2863,17 +3093,20 @@
       <c r="D73">
         <v>351</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E73">
+        <v>353</v>
+      </c>
+      <c r="F73" t="s">
         <v>63</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>38</v>
       </c>
-      <c r="G73" t="s">
+      <c r="H73" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>129</v>
       </c>
@@ -2886,17 +3119,20 @@
       <c r="D74">
         <v>350</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E74">
+        <v>352</v>
+      </c>
+      <c r="F74" t="s">
         <v>11</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
         <v>8</v>
       </c>
-      <c r="G74" t="s">
+      <c r="H74" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>129</v>
       </c>
@@ -2909,17 +3145,20 @@
       <c r="D75">
         <v>416</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E75">
+        <v>419</v>
+      </c>
+      <c r="F75" t="s">
         <v>34</v>
       </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>22</v>
       </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>129</v>
       </c>
@@ -2932,17 +3171,20 @@
       <c r="D76">
         <v>426</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E76">
+        <v>429</v>
+      </c>
+      <c r="F76" t="s">
         <v>21</v>
       </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
         <v>9</v>
       </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>129</v>
       </c>
@@ -2955,17 +3197,20 @@
       <c r="D77">
         <v>230</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E77">
+        <v>232</v>
+      </c>
+      <c r="F77" t="s">
         <v>18</v>
       </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>34</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>129</v>
       </c>
@@ -2978,17 +3223,20 @@
       <c r="D78">
         <v>351</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E78">
+        <v>353</v>
+      </c>
+      <c r="F78" t="s">
         <v>63</v>
       </c>
-      <c r="F78" t="s">
+      <c r="G78" t="s">
         <v>38</v>
       </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>129</v>
       </c>
@@ -3001,17 +3249,20 @@
       <c r="D79">
         <v>391</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E79">
+        <v>394</v>
+      </c>
+      <c r="F79" t="s">
         <v>18</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
         <v>35</v>
       </c>
-      <c r="G79" t="s">
+      <c r="H79" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>131</v>
       </c>
@@ -3024,17 +3275,20 @@
       <c r="D80">
         <v>298</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E80">
+        <v>347</v>
+      </c>
+      <c r="F80" t="s">
         <v>35</v>
       </c>
-      <c r="F80" t="s">
+      <c r="G80" t="s">
         <v>47</v>
       </c>
-      <c r="G80" t="s">
+      <c r="H80" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>131</v>
       </c>
@@ -3047,17 +3301,20 @@
       <c r="D81">
         <v>191</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E81">
+        <v>240</v>
+      </c>
+      <c r="F81" t="s">
         <v>19</v>
       </c>
-      <c r="F81" t="s">
+      <c r="G81" t="s">
         <v>8</v>
       </c>
-      <c r="G81" t="s">
+      <c r="H81" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>134</v>
       </c>
@@ -3070,17 +3327,20 @@
       <c r="D82">
         <v>102</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E82">
+        <v>102</v>
+      </c>
+      <c r="F82" t="s">
         <v>67</v>
       </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>15</v>
       </c>
-      <c r="G82" t="s">
+      <c r="H82" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>136</v>
       </c>
@@ -3093,17 +3353,20 @@
       <c r="D83">
         <v>53</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E83">
+        <v>53</v>
+      </c>
+      <c r="F83" t="s">
         <v>8</v>
       </c>
-      <c r="F83" t="s">
+      <c r="G83" t="s">
         <v>15</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>138</v>
       </c>
@@ -3116,17 +3379,20 @@
       <c r="D84">
         <v>114</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E84">
+        <v>307</v>
+      </c>
+      <c r="F84" t="s">
         <v>9</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>21</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>138</v>
       </c>
@@ -3139,17 +3405,20 @@
       <c r="D85">
         <v>115</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E85">
+        <v>308</v>
+      </c>
+      <c r="F85" t="s">
         <v>67</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>34</v>
       </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>138</v>
       </c>
@@ -3162,17 +3431,20 @@
       <c r="D86">
         <v>125</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E86">
+        <v>318</v>
+      </c>
+      <c r="F86" t="s">
         <v>37</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
         <v>42</v>
       </c>
-      <c r="G86" t="s">
+      <c r="H86" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>138</v>
       </c>
@@ -3185,17 +3457,20 @@
       <c r="D87">
         <v>117</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E87">
+        <v>310</v>
+      </c>
+      <c r="F87" t="s">
         <v>21</v>
       </c>
-      <c r="F87" t="s">
+      <c r="G87" t="s">
         <v>22</v>
       </c>
-      <c r="G87" t="s">
+      <c r="H87" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>138</v>
       </c>
@@ -3208,17 +3483,20 @@
       <c r="D88">
         <v>119</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E88">
+        <v>312</v>
+      </c>
+      <c r="F88" t="s">
         <v>34</v>
       </c>
-      <c r="F88" t="s">
+      <c r="G88" t="s">
         <v>22</v>
       </c>
-      <c r="G88" t="s">
+      <c r="H88" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>145</v>
       </c>
@@ -3231,17 +3509,20 @@
       <c r="D89">
         <v>46</v>
       </c>
-      <c r="E89" t="s">
+      <c r="E89">
+        <v>83</v>
+      </c>
+      <c r="F89" t="s">
         <v>38</v>
       </c>
-      <c r="F89" t="s">
+      <c r="G89" t="s">
         <v>22</v>
       </c>
-      <c r="G89" t="s">
+      <c r="H89" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>145</v>
       </c>
@@ -3254,17 +3535,20 @@
       <c r="D90">
         <v>583</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E90">
+        <v>631</v>
+      </c>
+      <c r="F90" t="s">
         <v>11</v>
       </c>
-      <c r="F90" t="s">
+      <c r="G90" t="s">
         <v>42</v>
       </c>
-      <c r="G90" t="s">
+      <c r="H90" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>145</v>
       </c>
@@ -3277,17 +3561,20 @@
       <c r="D91">
         <v>579</v>
       </c>
-      <c r="E91" t="s">
+      <c r="E91">
+        <v>627</v>
+      </c>
+      <c r="F91" t="s">
         <v>42</v>
       </c>
-      <c r="F91" t="s">
+      <c r="G91" t="s">
         <v>34</v>
       </c>
-      <c r="G91" t="s">
+      <c r="H91" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>145</v>
       </c>
@@ -3300,17 +3587,20 @@
       <c r="D92">
         <v>88</v>
       </c>
-      <c r="E92" t="s">
+      <c r="E92">
+        <v>125</v>
+      </c>
+      <c r="F92" t="s">
         <v>8</v>
       </c>
-      <c r="F92" t="s">
+      <c r="G92" t="s">
         <v>24</v>
       </c>
-      <c r="G92" t="s">
+      <c r="H92" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>145</v>
       </c>
@@ -3323,17 +3613,20 @@
       <c r="D93">
         <v>301</v>
       </c>
-      <c r="E93" t="s">
+      <c r="E93">
+        <v>343</v>
+      </c>
+      <c r="F93" t="s">
         <v>42</v>
       </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
         <v>18</v>
       </c>
-      <c r="G93" t="s">
+      <c r="H93" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>148</v>
       </c>
@@ -3346,17 +3639,20 @@
       <c r="D94">
         <v>35</v>
       </c>
-      <c r="E94" t="s">
+      <c r="E94">
+        <v>44</v>
+      </c>
+      <c r="F94" t="s">
         <v>9</v>
       </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>21</v>
       </c>
-      <c r="G94" t="s">
+      <c r="H94" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>148</v>
       </c>
@@ -3369,17 +3665,20 @@
       <c r="D95">
         <v>309</v>
       </c>
-      <c r="E95" t="s">
+      <c r="E95">
+        <v>446</v>
+      </c>
+      <c r="F95" t="s">
         <v>37</v>
       </c>
-      <c r="F95" t="s">
+      <c r="G95" t="s">
         <v>13</v>
       </c>
-      <c r="G95" t="s">
+      <c r="H95" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>148</v>
       </c>
@@ -3392,17 +3691,20 @@
       <c r="D96">
         <v>1</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E96">
+        <v>10</v>
+      </c>
+      <c r="F96" t="s">
         <v>19</v>
       </c>
-      <c r="F96" t="s">
+      <c r="G96" t="s">
         <v>9</v>
       </c>
-      <c r="G96" t="s">
+      <c r="H96" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>153</v>
       </c>
@@ -3415,17 +3717,20 @@
       <c r="D97">
         <v>372</v>
       </c>
-      <c r="E97" t="s">
+      <c r="E97">
+        <v>519</v>
+      </c>
+      <c r="F97" t="s">
         <v>8</v>
       </c>
-      <c r="F97" t="s">
+      <c r="G97" t="s">
         <v>63</v>
       </c>
-      <c r="G97" t="s">
+      <c r="H97" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>153</v>
       </c>
@@ -3438,17 +3743,20 @@
       <c r="D98">
         <v>167</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E98">
+        <v>297</v>
+      </c>
+      <c r="F98" t="s">
         <v>22</v>
       </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>9</v>
       </c>
-      <c r="G98" t="s">
+      <c r="H98" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>156</v>
       </c>
@@ -3461,17 +3769,20 @@
       <c r="D99">
         <v>780</v>
       </c>
-      <c r="E99" t="s">
+      <c r="E99">
+        <v>822</v>
+      </c>
+      <c r="F99" t="s">
         <v>34</v>
       </c>
-      <c r="F99" t="s">
+      <c r="G99" t="s">
         <v>22</v>
       </c>
-      <c r="G99" t="s">
+      <c r="H99" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>158</v>
       </c>
@@ -3484,17 +3795,20 @@
       <c r="D100">
         <v>164</v>
       </c>
-      <c r="E100" t="s">
+      <c r="E100">
+        <v>185</v>
+      </c>
+      <c r="F100" t="s">
         <v>101</v>
       </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
         <v>47</v>
       </c>
-      <c r="G100" t="s">
+      <c r="H100" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>158</v>
       </c>
@@ -3507,17 +3821,20 @@
       <c r="D101">
         <v>176</v>
       </c>
-      <c r="E101" t="s">
+      <c r="E101">
+        <v>197</v>
+      </c>
+      <c r="F101" t="s">
         <v>8</v>
       </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>15</v>
       </c>
-      <c r="G101" t="s">
+      <c r="H101" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>158</v>
       </c>
@@ -3530,17 +3847,20 @@
       <c r="D102">
         <v>413</v>
       </c>
-      <c r="E102" t="s">
+      <c r="E102">
+        <v>434</v>
+      </c>
+      <c r="F102" t="s">
         <v>8</v>
       </c>
-      <c r="F102" t="s">
+      <c r="G102" t="s">
         <v>11</v>
       </c>
-      <c r="G102" t="s">
+      <c r="H102" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>158</v>
       </c>
@@ -3553,17 +3873,20 @@
       <c r="D103">
         <v>156</v>
       </c>
-      <c r="E103" t="s">
+      <c r="E103">
+        <v>177</v>
+      </c>
+      <c r="F103" t="s">
         <v>35</v>
       </c>
-      <c r="F103" t="s">
+      <c r="G103" t="s">
         <v>34</v>
       </c>
-      <c r="G103" t="s">
+      <c r="H103" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>161</v>
       </c>
@@ -3576,17 +3899,20 @@
       <c r="D104">
         <v>271</v>
       </c>
-      <c r="E104" t="s">
+      <c r="E104">
+        <v>278</v>
+      </c>
+      <c r="F104" t="s">
         <v>8</v>
       </c>
-      <c r="F104" t="s">
+      <c r="G104" t="s">
         <v>21</v>
       </c>
-      <c r="G104" t="s">
+      <c r="H104" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>163</v>
       </c>
@@ -3599,17 +3925,20 @@
       <c r="D105">
         <v>1</v>
       </c>
-      <c r="E105" t="s">
+      <c r="E105">
+        <v>83</v>
+      </c>
+      <c r="F105" t="s">
         <v>19</v>
       </c>
-      <c r="F105" t="s">
+      <c r="G105" t="s">
         <v>9</v>
       </c>
-      <c r="G105" t="s">
+      <c r="H105" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>166</v>
       </c>
@@ -3622,17 +3951,20 @@
       <c r="D106">
         <v>760</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E106">
+        <v>765</v>
+      </c>
+      <c r="F106" t="s">
         <v>8</v>
       </c>
-      <c r="F106" t="s">
+      <c r="G106" t="s">
         <v>11</v>
       </c>
-      <c r="G106" t="s">
+      <c r="H106" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>168</v>
       </c>
@@ -3645,17 +3977,20 @@
       <c r="D107">
         <v>237</v>
       </c>
-      <c r="E107" t="s">
+      <c r="E107">
+        <v>271</v>
+      </c>
+      <c r="F107" t="s">
         <v>47</v>
       </c>
-      <c r="F107" t="s">
+      <c r="G107" t="s">
         <v>8</v>
       </c>
-      <c r="G107" t="s">
+      <c r="H107" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>168</v>
       </c>
@@ -3668,17 +4003,20 @@
       <c r="D108">
         <v>239</v>
       </c>
-      <c r="E108" t="s">
+      <c r="E108">
+        <v>273</v>
+      </c>
+      <c r="F108" t="s">
         <v>8</v>
       </c>
-      <c r="F108" t="s">
+      <c r="G108" t="s">
         <v>22</v>
       </c>
-      <c r="G108" t="s">
+      <c r="H108" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>171</v>
       </c>
@@ -3691,17 +4029,20 @@
       <c r="D109">
         <v>1021</v>
       </c>
-      <c r="E109" t="s">
+      <c r="E109">
+        <v>1342</v>
+      </c>
+      <c r="F109" t="s">
         <v>8</v>
       </c>
-      <c r="F109" t="s">
+      <c r="G109" t="s">
         <v>63</v>
       </c>
-      <c r="G109" t="s">
+      <c r="H109" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>174</v>
       </c>
@@ -3714,17 +4055,20 @@
       <c r="D110">
         <v>793</v>
       </c>
-      <c r="E110" t="s">
+      <c r="E110">
+        <v>808</v>
+      </c>
+      <c r="F110" t="s">
         <v>8</v>
       </c>
-      <c r="F110" t="s">
+      <c r="G110" t="s">
         <v>34</v>
       </c>
-      <c r="G110" t="s">
+      <c r="H110" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>176</v>
       </c>
@@ -3737,17 +4081,20 @@
       <c r="D111">
         <v>1</v>
       </c>
-      <c r="E111" t="s">
+      <c r="E111">
+        <v>54</v>
+      </c>
+      <c r="F111" t="s">
         <v>19</v>
       </c>
-      <c r="F111" t="s">
+      <c r="G111" t="s">
         <v>47</v>
       </c>
-      <c r="G111" t="s">
+      <c r="H111" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>179</v>
       </c>
@@ -3760,17 +4107,20 @@
       <c r="D112">
         <v>422</v>
       </c>
-      <c r="E112" t="s">
+      <c r="E112">
+        <v>429</v>
+      </c>
+      <c r="F112" t="s">
         <v>18</v>
       </c>
-      <c r="F112" t="s">
+      <c r="G112" t="s">
         <v>101</v>
       </c>
-      <c r="G112" t="s">
+      <c r="H112" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>182</v>
       </c>
@@ -3783,17 +4133,20 @@
       <c r="D113">
         <v>815</v>
       </c>
-      <c r="E113" t="s">
+      <c r="E113">
+        <v>830</v>
+      </c>
+      <c r="F113" t="s">
         <v>101</v>
       </c>
-      <c r="F113" t="s">
+      <c r="G113" t="s">
         <v>47</v>
       </c>
-      <c r="G113" t="s">
+      <c r="H113" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>185</v>
       </c>
@@ -3806,17 +4159,20 @@
       <c r="D114">
         <v>92</v>
       </c>
-      <c r="E114" t="s">
+      <c r="E114">
+        <v>92</v>
+      </c>
+      <c r="F114" t="s">
         <v>34</v>
       </c>
-      <c r="F114" t="s">
+      <c r="G114" t="s">
         <v>8</v>
       </c>
-      <c r="G114" t="s">
+      <c r="H114" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>188</v>
       </c>
@@ -3829,17 +4185,20 @@
       <c r="D115">
         <v>142</v>
       </c>
-      <c r="E115" t="s">
+      <c r="E115">
+        <v>142</v>
+      </c>
+      <c r="F115" t="s">
         <v>18</v>
       </c>
-      <c r="F115" t="s">
+      <c r="G115" t="s">
         <v>101</v>
       </c>
-      <c r="G115" t="s">
+      <c r="H115" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>188</v>
       </c>
@@ -3852,17 +4211,20 @@
       <c r="D116">
         <v>127</v>
       </c>
-      <c r="E116" t="s">
+      <c r="E116">
+        <v>127</v>
+      </c>
+      <c r="F116" t="s">
         <v>101</v>
       </c>
-      <c r="F116" t="s">
+      <c r="G116" t="s">
         <v>18</v>
       </c>
-      <c r="G116" t="s">
+      <c r="H116" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>188</v>
       </c>
@@ -3875,17 +4237,20 @@
       <c r="D117">
         <v>82</v>
       </c>
-      <c r="E117" t="s">
+      <c r="E117">
+        <v>82</v>
+      </c>
+      <c r="F117" t="s">
         <v>67</v>
       </c>
-      <c r="F117" t="s">
+      <c r="G117" t="s">
         <v>24</v>
       </c>
-      <c r="G117" t="s">
+      <c r="H117" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>188</v>
       </c>
@@ -3898,17 +4263,20 @@
       <c r="D118">
         <v>77</v>
       </c>
-      <c r="E118" t="s">
+      <c r="E118">
+        <v>77</v>
+      </c>
+      <c r="F118" t="s">
         <v>34</v>
       </c>
-      <c r="F118" t="s">
+      <c r="G118" t="s">
         <v>8</v>
       </c>
-      <c r="G118" t="s">
+      <c r="H118" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>188</v>
       </c>
@@ -3921,17 +4289,20 @@
       <c r="D119">
         <v>126</v>
       </c>
-      <c r="E119" t="s">
+      <c r="E119">
+        <v>126</v>
+      </c>
+      <c r="F119" t="s">
         <v>47</v>
       </c>
-      <c r="F119" t="s">
+      <c r="G119" t="s">
         <v>101</v>
       </c>
-      <c r="G119" t="s">
+      <c r="H119" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>190</v>
       </c>
@@ -3944,17 +4315,20 @@
       <c r="D120">
         <v>3719</v>
       </c>
-      <c r="E120" t="s">
+      <c r="E120">
+        <v>3733</v>
+      </c>
+      <c r="F120" t="s">
         <v>8</v>
       </c>
-      <c r="F120" t="s">
+      <c r="G120" t="s">
         <v>38</v>
       </c>
-      <c r="G120" t="s">
+      <c r="H120" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>192</v>
       </c>
@@ -3967,17 +4341,20 @@
       <c r="D121">
         <v>151</v>
       </c>
-      <c r="E121" t="s">
+      <c r="E121">
+        <v>216</v>
+      </c>
+      <c r="F121" t="s">
         <v>101</v>
       </c>
-      <c r="F121" t="s">
+      <c r="G121" t="s">
         <v>9</v>
       </c>
-      <c r="G121" t="s">
+      <c r="H121" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>192</v>
       </c>
@@ -3990,17 +4367,20 @@
       <c r="D122">
         <v>132</v>
       </c>
-      <c r="E122" t="s">
+      <c r="E122">
+        <v>195</v>
+      </c>
+      <c r="F122" t="s">
         <v>15</v>
       </c>
-      <c r="F122" t="s">
+      <c r="G122" t="s">
         <v>21</v>
       </c>
-      <c r="G122" t="s">
+      <c r="H122" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>192</v>
       </c>
@@ -4013,17 +4393,20 @@
       <c r="D123">
         <v>154</v>
       </c>
-      <c r="E123" t="s">
+      <c r="E123">
+        <v>219</v>
+      </c>
+      <c r="F123" t="s">
         <v>21</v>
       </c>
-      <c r="F123" t="s">
+      <c r="G123" t="s">
         <v>35</v>
       </c>
-      <c r="G123" t="s">
+      <c r="H123" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>192</v>
       </c>
@@ -4036,17 +4419,20 @@
       <c r="D124">
         <v>114</v>
       </c>
-      <c r="E124" t="s">
+      <c r="E124">
+        <v>177</v>
+      </c>
+      <c r="F124" t="s">
         <v>34</v>
       </c>
-      <c r="F124" t="s">
+      <c r="G124" t="s">
         <v>22</v>
       </c>
-      <c r="G124" t="s">
+      <c r="H124" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>192</v>
       </c>
@@ -4059,17 +4445,20 @@
       <c r="D125">
         <v>161</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E125">
+        <v>226</v>
+      </c>
+      <c r="F125" t="s">
         <v>8</v>
       </c>
-      <c r="F125" t="s">
+      <c r="G125" t="s">
         <v>34</v>
       </c>
-      <c r="G125" t="s">
+      <c r="H125" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>192</v>
       </c>
@@ -4082,17 +4471,20 @@
       <c r="D126">
         <v>170</v>
       </c>
-      <c r="E126" t="s">
+      <c r="E126">
+        <v>244</v>
+      </c>
+      <c r="F126" t="s">
         <v>18</v>
       </c>
-      <c r="F126" t="s">
+      <c r="G126" t="s">
         <v>9</v>
       </c>
-      <c r="G126" t="s">
+      <c r="H126" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>194</v>
       </c>
@@ -4105,17 +4497,20 @@
       <c r="D127">
         <v>528</v>
       </c>
-      <c r="E127" t="s">
+      <c r="E127">
+        <v>563</v>
+      </c>
+      <c r="F127" t="s">
         <v>95</v>
       </c>
-      <c r="F127" t="s">
+      <c r="G127" t="s">
         <v>22</v>
       </c>
-      <c r="G127" t="s">
+      <c r="H127" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>196</v>
       </c>
@@ -4128,17 +4523,20 @@
       <c r="D128">
         <v>341</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E128">
+        <v>523</v>
+      </c>
+      <c r="F128" t="s">
         <v>22</v>
       </c>
-      <c r="F128" t="s">
+      <c r="G128" t="s">
         <v>34</v>
       </c>
-      <c r="G128" t="s">
+      <c r="H128" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>198</v>
       </c>
@@ -4151,13 +4549,16 @@
       <c r="D129">
         <v>1049</v>
       </c>
-      <c r="E129" t="s">
+      <c r="E129">
+        <v>1091</v>
+      </c>
+      <c r="F129" t="s">
         <v>11</v>
       </c>
-      <c r="F129" t="s">
+      <c r="G129" t="s">
         <v>8</v>
       </c>
-      <c r="G129" t="s">
+      <c r="H129" t="s">
         <v>57</v>
       </c>
     </row>

--- a/Outputs_primates/AllGenes_Potential_CPDs.xlsx
+++ b/Outputs_primates/AllGenes_Potential_CPDs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adesinamary/Documents/GitHub/kondrashov/Outputs_primates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1074AAF9-0BC4-B749-96F9-6249F1D83E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2AFB6C-B6BE-D242-8FA1-EF65A1680E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="12560" windowWidth="21480" windowHeight="13260" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
+    <workbookView xWindow="940" yWindow="12540" windowWidth="20520" windowHeight="13260" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Outputs_primates/AllGenes_Potential_CPDs.xlsx
+++ b/Outputs_primates/AllGenes_Potential_CPDs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adesinamary/Documents/GitHub/kondrashov/Outputs_primates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uofh-my.sharepoint.com/personal/miadesin_cougarnet_uh_edu/Documents/Documents/Ricardo_lab/GitHub/kondrashov/Outputs_primates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2AFB6C-B6BE-D242-8FA1-EF65A1680E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{8A2AFB6C-B6BE-D242-8FA1-EF65A1680E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DB285DF-C76F-4595-AE27-BADC09324134}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="12540" windowWidth="20520" windowHeight="13260" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{BC6F7999-E049-F441-AF63-5F5D062E3B8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="262">
   <si>
     <t>gene</t>
   </si>
@@ -822,6 +822,21 @@
   </si>
   <si>
     <t>Aln</t>
+  </si>
+  <si>
+    <t>P XP_012516579.1 Propithecus coquereli
+P XP_012657175.1 Otolemur garnettii
+P XP_053447073.1 Nycticebus coucang
+- XP_008053273.1 Carlito syrichta
+P XP_012643243.1 Microcebus murinus
+P XP_045403682.1 Lemur catta
+P XP_069334191.1 Eulemur rufifrons
+L XP_064228588.1 Aotus nancymaae
+- XP_037595556.1 Cebus imitator
+L XP_039329541.1 Saimiri boliviensis
+L XP_035107801.2 Callithrix jacchus
+L XP_032152462.1 Sapajus apella
+Q XP_032011454.1 Hylobates moloch</t>
   </si>
 </sst>
 </file>
@@ -864,9 +879,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1201,14 +1219,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81CD1290-D98E-6145-998E-728A92BEC841}">
-  <dimension ref="A1:I129"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J129"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.796875" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="10" max="10" width="55.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1237,7 +1256,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="202.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1265,8 +1284,11 @@
       <c r="I2">
         <v>34</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J2" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1292,7 +1314,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1318,7 +1340,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1344,7 +1366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1370,7 +1392,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1396,7 +1418,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1422,7 +1444,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1448,7 +1470,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1474,7 +1496,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -1500,7 +1522,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>29</v>
       </c>
@@ -1526,7 +1548,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -1552,7 +1574,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>32</v>
       </c>
@@ -1578,7 +1600,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>32</v>
       </c>
@@ -1604,7 +1626,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1630,7 +1652,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>44</v>
       </c>
@@ -1656,7 +1678,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -1682,7 +1704,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>49</v>
       </c>
@@ -1708,7 +1730,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -1734,7 +1756,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1760,7 +1782,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>49</v>
       </c>
@@ -1786,7 +1808,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -1812,7 +1834,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -1838,7 +1860,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>54</v>
       </c>
@@ -1864,7 +1886,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1890,7 +1912,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>54</v>
       </c>
@@ -1916,7 +1938,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>54</v>
       </c>
@@ -1942,7 +1964,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>59</v>
       </c>
@@ -1968,7 +1990,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>59</v>
       </c>
@@ -1994,7 +2016,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -2020,7 +2042,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>59</v>
       </c>
@@ -2046,7 +2068,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>65</v>
       </c>
@@ -2072,7 +2094,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>65</v>
       </c>
@@ -2098,7 +2120,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>65</v>
       </c>
@@ -2124,7 +2146,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>68</v>
       </c>
@@ -2150,7 +2172,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>68</v>
       </c>
@@ -2176,7 +2198,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>71</v>
       </c>
@@ -2202,7 +2224,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -2228,7 +2250,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -2254,7 +2276,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>77</v>
       </c>
@@ -2280,7 +2302,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>77</v>
       </c>
@@ -2306,7 +2328,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>80</v>
       </c>
@@ -2332,7 +2354,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -2358,7 +2380,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>82</v>
       </c>
@@ -2384,7 +2406,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>86</v>
       </c>
@@ -2410,7 +2432,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>88</v>
       </c>
@@ -2436,7 +2458,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>88</v>
       </c>
@@ -2462,7 +2484,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>91</v>
       </c>
@@ -2488,7 +2510,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>93</v>
       </c>
@@ -2514,7 +2536,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>93</v>
       </c>
@@ -2540,7 +2562,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>93</v>
       </c>
@@ -2566,7 +2588,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>99</v>
       </c>
@@ -2589,7 +2611,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>103</v>
       </c>
@@ -2615,7 +2637,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>105</v>
       </c>
@@ -2641,7 +2663,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -2667,7 +2689,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>110</v>
       </c>
@@ -2693,7 +2715,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>110</v>
       </c>
@@ -2719,7 +2741,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>113</v>
       </c>
@@ -2745,7 +2767,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>115</v>
       </c>
@@ -2771,7 +2793,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>115</v>
       </c>
@@ -2797,7 +2819,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>117</v>
       </c>
@@ -2823,7 +2845,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>120</v>
       </c>
@@ -2849,7 +2871,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>122</v>
       </c>
@@ -2872,7 +2894,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>122</v>
       </c>
@@ -2898,7 +2920,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>122</v>
       </c>
@@ -2924,7 +2946,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>122</v>
       </c>
@@ -2950,7 +2972,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>122</v>
       </c>
@@ -2976,7 +2998,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>126</v>
       </c>
@@ -3002,7 +3024,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>129</v>
       </c>
@@ -3028,7 +3050,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>129</v>
       </c>
@@ -3054,7 +3076,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>129</v>
       </c>
@@ -3080,7 +3102,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>129</v>
       </c>
@@ -3106,7 +3128,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>129</v>
       </c>
@@ -3132,7 +3154,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>129</v>
       </c>
@@ -3158,7 +3180,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>129</v>
       </c>
@@ -3184,7 +3206,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>129</v>
       </c>
@@ -3210,7 +3232,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>129</v>
       </c>
@@ -3236,7 +3258,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>129</v>
       </c>
@@ -3262,7 +3284,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>131</v>
       </c>
@@ -3288,7 +3310,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>131</v>
       </c>
@@ -3314,7 +3336,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>134</v>
       </c>
@@ -3340,7 +3362,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>136</v>
       </c>
@@ -3366,7 +3388,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>138</v>
       </c>
@@ -3392,7 +3414,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>138</v>
       </c>
@@ -3418,7 +3440,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>138</v>
       </c>
@@ -3444,7 +3466,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>138</v>
       </c>
@@ -3470,7 +3492,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>138</v>
       </c>
@@ -3496,7 +3518,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>145</v>
       </c>
@@ -3522,7 +3544,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>145</v>
       </c>
@@ -3548,7 +3570,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>145</v>
       </c>
@@ -3574,7 +3596,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>145</v>
       </c>
@@ -3600,7 +3622,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>145</v>
       </c>
@@ -3626,7 +3648,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>148</v>
       </c>
@@ -3652,7 +3674,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>148</v>
       </c>
@@ -3678,7 +3700,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>148</v>
       </c>
@@ -3704,7 +3726,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>153</v>
       </c>
@@ -3730,7 +3752,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>153</v>
       </c>
@@ -3756,7 +3778,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>156</v>
       </c>
@@ -3782,7 +3804,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>158</v>
       </c>
@@ -3808,7 +3830,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>158</v>
       </c>
@@ -3834,7 +3856,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>158</v>
       </c>
@@ -3860,7 +3882,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>158</v>
       </c>
@@ -3886,7 +3908,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>161</v>
       </c>
@@ -3912,7 +3934,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>163</v>
       </c>
@@ -3938,7 +3960,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>166</v>
       </c>
@@ -3964,7 +3986,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>168</v>
       </c>
@@ -3990,7 +4012,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>168</v>
       </c>
@@ -4016,7 +4038,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>171</v>
       </c>
@@ -4042,7 +4064,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>174</v>
       </c>
@@ -4068,7 +4090,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>176</v>
       </c>
@@ -4094,7 +4116,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>179</v>
       </c>
@@ -4120,7 +4142,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>182</v>
       </c>
@@ -4146,7 +4168,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>185</v>
       </c>
@@ -4172,7 +4194,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>188</v>
       </c>
@@ -4198,7 +4220,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>188</v>
       </c>
@@ -4224,7 +4246,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>188</v>
       </c>
@@ -4250,7 +4272,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>188</v>
       </c>
@@ -4276,7 +4298,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>188</v>
       </c>
@@ -4302,7 +4324,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>190</v>
       </c>
@@ -4328,7 +4350,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>192</v>
       </c>
@@ -4354,7 +4376,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>192</v>
       </c>
@@ -4380,7 +4402,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>192</v>
       </c>
@@ -4406,7 +4428,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>192</v>
       </c>
@@ -4432,7 +4454,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>192</v>
       </c>
@@ -4458,7 +4480,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>192</v>
       </c>
@@ -4484,7 +4506,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>194</v>
       </c>
@@ -4510,7 +4532,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>196</v>
       </c>
@@ -4536,7 +4558,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>198</v>
       </c>
